--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8900CA1-7474-4335-A473-EA368205F96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0520ABD0-1E9E-41DB-8F1A-5401F924F061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0520ABD0-1E9E-41DB-8F1A-5401F924F061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A24FB6F-C7F4-4682-97D6-898E8698DF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A24FB6F-C7F4-4682-97D6-898E8698DF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D210DF1-BEFB-47B9-82C4-31372107CD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D210DF1-BEFB-47B9-82C4-31372107CD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02FB371-003E-4E91-8BE9-D9F20D41476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02FB371-003E-4E91-8BE9-D9F20D41476E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7016E-5AC3-44A5-8855-5FCEA3CE386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7016E-5AC3-44A5-8855-5FCEA3CE386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A4E166-FD3E-4ECA-90F2-95097FA42024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A4E166-FD3E-4ECA-90F2-95097FA42024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09ABA64-43E6-47CC-9AFB-219DD0CFA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09ABA64-43E6-47CC-9AFB-219DD0CFA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA14AB-DA28-42F9-8C04-79B7D3BEC64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA14AB-DA28-42F9-8C04-79B7D3BEC64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D36B7-6A75-421A-A522-55EF6AD0DFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D36B7-6A75-421A-A522-55EF6AD0DFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B256CA-ADF9-4CC5-8C60-E2A70C67421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,202 +52,190 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
-    <t>ABDRAMAN IBRAHIM</t>
-  </si>
-  <si>
-    <t>Saladin</t>
-  </si>
-  <si>
-    <t>05/07/1950</t>
-  </si>
-  <si>
-    <t>Kenya</t>
+    <t>AMRANI</t>
+  </si>
+  <si>
+    <t>Abdulkadir Mohamed</t>
+  </si>
+  <si>
+    <t>04/04/1975</t>
+  </si>
+  <si>
+    <t>Tanzannie</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>BATOL</t>
+  </si>
+  <si>
+    <t>Hassan</t>
+  </si>
+  <si>
+    <t>15/05/1997</t>
+  </si>
+  <si>
+    <t>Soudan</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>BEZHANISHVILI</t>
+  </si>
+  <si>
+    <t>Zurab</t>
+  </si>
+  <si>
+    <t>30/06/1974</t>
+  </si>
+  <si>
+    <t>Géorgie</t>
+  </si>
+  <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
+    <t>BOUZID</t>
+  </si>
+  <si>
+    <t>Bouchra</t>
+  </si>
+  <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>KALANDIA</t>
+  </si>
+  <si>
+    <t>Tamar</t>
+  </si>
+  <si>
+    <t>09/10/1979</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
+  </si>
+  <si>
+    <t>KHACHATRYAN</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>21/01/1973</t>
+  </si>
+  <si>
+    <t>Arménie</t>
+  </si>
+  <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
+    <t>KHUTSISHVILI</t>
+  </si>
+  <si>
+    <t>Rusudan</t>
+  </si>
+  <si>
+    <t>08/11/1987</t>
+  </si>
+  <si>
+    <t>LENGO</t>
+  </si>
+  <si>
+    <t>Lucoqui</t>
+  </si>
+  <si>
+    <t>07/11/1984</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>24/04/2025</t>
+  </si>
+  <si>
+    <t>MAMBA</t>
+  </si>
+  <si>
+    <t>Benayi</t>
+  </si>
+  <si>
+    <t>15/07/1985</t>
+  </si>
+  <si>
+    <t>12/09/2024</t>
+  </si>
+  <si>
+    <t>MANTUIKA</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>MEHMOOD</t>
+  </si>
+  <si>
+    <t>Aamir</t>
+  </si>
+  <si>
+    <t>15/05/1990</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
+    <t>MIAH</t>
+  </si>
+  <si>
+    <t>Mowab</t>
+  </si>
+  <si>
+    <t>28/05/1995</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
+    <t>MOHAMED EL NOUR</t>
+  </si>
+  <si>
+    <t>Abdel</t>
+  </si>
+  <si>
+    <t>19/01/1977</t>
+  </si>
+  <si>
     <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
-    <t>AMRANI</t>
-  </si>
-  <si>
-    <t>Abdulkadir Mohamed</t>
-  </si>
-  <si>
-    <t>04/04/1975</t>
-  </si>
-  <si>
-    <t>Tanzannie</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>BATOL</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>15/05/1997</t>
-  </si>
-  <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>01/09/2024</t>
-  </si>
-  <si>
-    <t>BEZHANISHVILI</t>
-  </si>
-  <si>
-    <t>Zurab</t>
-  </si>
-  <si>
-    <t>30/06/1974</t>
-  </si>
-  <si>
-    <t>Géorgie</t>
-  </si>
-  <si>
-    <t>06/02/2025</t>
-  </si>
-  <si>
-    <t>BOUZID</t>
-  </si>
-  <si>
-    <t>Bouchra</t>
-  </si>
-  <si>
-    <t>01/01/1983</t>
-  </si>
-  <si>
-    <t>Maroc</t>
-  </si>
-  <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
-    <t>KALANDIA</t>
-  </si>
-  <si>
-    <t>Tamar</t>
-  </si>
-  <si>
-    <t>09/10/1979</t>
-  </si>
-  <si>
-    <t>22/05/2024</t>
-  </si>
-  <si>
-    <t>KHACHATRYAN</t>
-  </si>
-  <si>
-    <t>Rita</t>
-  </si>
-  <si>
-    <t>21/01/1973</t>
-  </si>
-  <si>
-    <t>Arménie</t>
-  </si>
-  <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
-    <t>KHUTSISHVILI</t>
-  </si>
-  <si>
-    <t>Rusudan</t>
-  </si>
-  <si>
-    <t>08/11/1987</t>
-  </si>
-  <si>
-    <t>LENGO</t>
-  </si>
-  <si>
-    <t>Lucoqui</t>
-  </si>
-  <si>
-    <t>07/11/1984</t>
-  </si>
-  <si>
-    <t>Angola</t>
-  </si>
-  <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
-    <t>MAMBA</t>
-  </si>
-  <si>
-    <t>Benayi</t>
-  </si>
-  <si>
-    <t>15/07/1985</t>
-  </si>
-  <si>
-    <t>12/09/2024</t>
-  </si>
-  <si>
-    <t>MANTUIKA</t>
-  </si>
-  <si>
-    <t>Sara</t>
-  </si>
-  <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>MEHMOOD</t>
-  </si>
-  <si>
-    <t>Aamir</t>
-  </si>
-  <si>
-    <t>15/05/1990</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
-    <t>MIAH</t>
-  </si>
-  <si>
-    <t>Mowab</t>
-  </si>
-  <si>
-    <t>28/05/1995</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
-    <t>MOHAMED EL NOUR</t>
-  </si>
-  <si>
-    <t>Abdel</t>
-  </si>
-  <si>
-    <t>19/01/1977</t>
   </si>
   <si>
     <t>MOHD</t>
@@ -1032,13 +1020,13 @@
         <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -1049,19 +1037,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>40</v>
@@ -1084,13 +1072,13 @@
         <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -1101,22 +1089,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="E11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="F11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1136,13 +1124,13 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -1153,22 +1141,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1179,16 +1167,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
@@ -1217,7 +1205,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
@@ -1240,13 +1228,13 @@
         <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1257,22 +1245,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F17" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1283,22 +1271,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -1309,22 +1297,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -1335,22 +1323,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -1361,22 +1349,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>92</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -1396,13 +1384,13 @@
         <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -1451,10 +1439,10 @@
         <v>104</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -1480,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -1491,52 +1479,38 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A27" s="4">
+      <c r="A27" s="11">
         <v>24</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A28" s="11">

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B256CA-ADF9-4CC5-8C60-E2A70C67421D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D75D0D-B080-431B-9F3C-726D2FE22371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D75D0D-B080-431B-9F3C-726D2FE22371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2776FD-0797-4882-89C8-8A8608A8CF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="74">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Abdulkadir Mohamed</t>
   </si>
   <si>
-    <t>04/04/1975</t>
+    <t/>
   </si>
   <si>
     <t>Tanzannie</t>
@@ -67,252 +67,147 @@
     <t>M</t>
   </si>
   <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>BATOL</t>
   </si>
   <si>
     <t>Hassan</t>
   </si>
   <si>
-    <t>15/05/1997</t>
-  </si>
-  <si>
     <t>Soudan</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>01/09/2024</t>
-  </si>
-  <si>
     <t>BEZHANISHVILI</t>
   </si>
   <si>
     <t>Zurab</t>
   </si>
   <si>
-    <t>30/06/1974</t>
-  </si>
-  <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>06/02/2025</t>
-  </si>
-  <si>
     <t>BOUZID</t>
   </si>
   <si>
     <t>Bouchra</t>
   </si>
   <si>
-    <t>01/01/1983</t>
-  </si>
-  <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
     <t>KALANDIA</t>
   </si>
   <si>
     <t>Tamar</t>
   </si>
   <si>
-    <t>09/10/1979</t>
-  </si>
-  <si>
-    <t>22/05/2024</t>
-  </si>
-  <si>
     <t>KHACHATRYAN</t>
   </si>
   <si>
     <t>Rita</t>
   </si>
   <si>
-    <t>21/01/1973</t>
-  </si>
-  <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>01/10/2024</t>
-  </si>
-  <si>
     <t>KHUTSISHVILI</t>
   </si>
   <si>
     <t>Rusudan</t>
   </si>
   <si>
-    <t>08/11/1987</t>
-  </si>
-  <si>
     <t>LENGO</t>
   </si>
   <si>
     <t>Lucoqui</t>
   </si>
   <si>
-    <t>07/11/1984</t>
-  </si>
-  <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
     <t>MAMBA</t>
   </si>
   <si>
     <t>Benayi</t>
   </si>
   <si>
-    <t>15/07/1985</t>
-  </si>
-  <si>
-    <t>12/09/2024</t>
-  </si>
-  <si>
     <t>MANTUIKA</t>
   </si>
   <si>
     <t>Sara</t>
   </si>
   <si>
-    <t>15/12/1999</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
     <t>MEHMOOD</t>
   </si>
   <si>
     <t>Aamir</t>
   </si>
   <si>
-    <t>15/05/1990</t>
-  </si>
-  <si>
     <t>Pakistan</t>
   </si>
   <si>
-    <t>12/01/2025</t>
-  </si>
-  <si>
     <t>MIAH</t>
   </si>
   <si>
     <t>Mowab</t>
   </si>
   <si>
-    <t>28/05/1995</t>
-  </si>
-  <si>
     <t>Bangladesh</t>
   </si>
   <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
     <t>MOHAMED EL NOUR</t>
   </si>
   <si>
     <t>Abdel</t>
   </si>
   <si>
-    <t>19/01/1977</t>
-  </si>
-  <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
     <t>MOHD</t>
   </si>
   <si>
     <t>Azeem Pacha</t>
   </si>
   <si>
-    <t>04/04/1991</t>
-  </si>
-  <si>
     <t>Inde</t>
   </si>
   <si>
-    <t>21/01/2025</t>
-  </si>
-  <si>
     <t>NDUGBE</t>
   </si>
   <si>
     <t>Josiah</t>
   </si>
   <si>
-    <t>10/10/1982</t>
-  </si>
-  <si>
     <t>Nigéria</t>
   </si>
   <si>
-    <t>19/11/2023</t>
-  </si>
-  <si>
     <t>NEHREBA</t>
   </si>
   <si>
     <t>Iryna</t>
   </si>
   <si>
-    <t>28/02/1987</t>
-  </si>
-  <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>21/11/2024</t>
-  </si>
-  <si>
     <t>OMAR</t>
   </si>
   <si>
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
     <t>OVERCHENKO</t>
   </si>
   <si>
     <t>Aleksandrova</t>
   </si>
   <si>
-    <t>30/09/1971</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
     <t>PINTO</t>
   </si>
   <si>
     <t>Janet</t>
   </si>
   <si>
-    <t>23/02/1971</t>
-  </si>
-  <si>
     <t>Pérou</t>
   </si>
   <si>
@@ -322,9 +217,6 @@
     <t>Daleep</t>
   </si>
   <si>
-    <t>01/09/1984</t>
-  </si>
-  <si>
     <t>Afghanistan</t>
   </si>
   <si>
@@ -334,9 +226,6 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998</t>
-  </si>
-  <si>
     <t>Somalie</t>
   </si>
   <si>
@@ -346,22 +235,13 @@
     <t>Malika</t>
   </si>
   <si>
-    <t>01/09/1956</t>
-  </si>
-  <si>
     <t>Espagne</t>
   </si>
   <si>
-    <t>16/11/2023</t>
-  </si>
-  <si>
     <t>YLDIRIM DOGAN</t>
   </si>
   <si>
     <t>Ozgun</t>
-  </si>
-  <si>
-    <t>01/07/1979</t>
   </si>
   <si>
     <t>Turquie</t>
@@ -922,10 +802,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -933,25 +813,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="G5" s="10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -959,25 +839,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -985,25 +865,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1011,25 +891,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1037,25 +917,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1063,25 +943,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1089,25 +969,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1115,25 +995,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1141,25 +1021,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1167,25 +1047,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1193,25 +1073,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1219,25 +1099,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1245,25 +1125,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1271,25 +1151,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1297,25 +1177,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1323,25 +1203,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1349,25 +1229,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1375,25 +1255,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1401,25 +1281,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1427,25 +1307,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1453,25 +1333,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1479,25 +1359,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2776FD-0797-4882-89C8-8A8608A8CF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6EA6D0-FD8E-4C10-A0EC-C93E19DFB076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_3.xlsx
+++ b/Excel/liste_groupe_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6EA6D0-FD8E-4C10-A0EC-C93E19DFB076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA71DCC-757A-47A8-8E2A-BB6EBDE01449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="114">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Abdulkadir Mohamed</t>
   </si>
   <si>
-    <t/>
+    <t>04/04/1975</t>
   </si>
   <si>
     <t>Tanzannie</t>
@@ -67,147 +67,252 @@
     <t>M</t>
   </si>
   <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>BATOL</t>
   </si>
   <si>
     <t>Hassan</t>
   </si>
   <si>
+    <t>15/05/1997</t>
+  </si>
+  <si>
     <t>Soudan</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
     <t>BEZHANISHVILI</t>
   </si>
   <si>
     <t>Zurab</t>
   </si>
   <si>
+    <t>30/06/1974</t>
+  </si>
+  <si>
     <t>Géorgie</t>
   </si>
   <si>
+    <t>06/02/2025</t>
+  </si>
+  <si>
     <t>BOUZID</t>
   </si>
   <si>
     <t>Bouchra</t>
   </si>
   <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
     <t>Maroc</t>
   </si>
   <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
     <t>KALANDIA</t>
   </si>
   <si>
     <t>Tamar</t>
   </si>
   <si>
+    <t>09/10/1979</t>
+  </si>
+  <si>
+    <t>22/05/2024</t>
+  </si>
+  <si>
     <t>KHACHATRYAN</t>
   </si>
   <si>
     <t>Rita</t>
   </si>
   <si>
+    <t>21/01/1973</t>
+  </si>
+  <si>
     <t>Arménie</t>
   </si>
   <si>
+    <t>01/10/2024</t>
+  </si>
+  <si>
     <t>KHUTSISHVILI</t>
   </si>
   <si>
     <t>Rusudan</t>
   </si>
   <si>
+    <t>08/11/1987</t>
+  </si>
+  <si>
     <t>LENGO</t>
   </si>
   <si>
     <t>Lucoqui</t>
   </si>
   <si>
+    <t>07/11/1984</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
+    <t>24/04/2025</t>
+  </si>
+  <si>
     <t>MAMBA</t>
   </si>
   <si>
     <t>Benayi</t>
   </si>
   <si>
+    <t>15/07/1985</t>
+  </si>
+  <si>
+    <t>12/09/2024</t>
+  </si>
+  <si>
     <t>MANTUIKA</t>
   </si>
   <si>
     <t>Sara</t>
   </si>
   <si>
+    <t>15/12/1999</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
     <t>MEHMOOD</t>
   </si>
   <si>
     <t>Aamir</t>
   </si>
   <si>
+    <t>15/05/1990</t>
+  </si>
+  <si>
     <t>Pakistan</t>
   </si>
   <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
     <t>MIAH</t>
   </si>
   <si>
     <t>Mowab</t>
   </si>
   <si>
+    <t>28/05/1995</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
     <t>MOHAMED EL NOUR</t>
   </si>
   <si>
     <t>Abdel</t>
   </si>
   <si>
+    <t>19/01/1977</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
     <t>MOHD</t>
   </si>
   <si>
     <t>Azeem Pacha</t>
   </si>
   <si>
+    <t>04/04/1991</t>
+  </si>
+  <si>
     <t>Inde</t>
   </si>
   <si>
+    <t>21/01/2025</t>
+  </si>
+  <si>
     <t>NDUGBE</t>
   </si>
   <si>
     <t>Josiah</t>
   </si>
   <si>
+    <t>10/10/1982</t>
+  </si>
+  <si>
     <t>Nigéria</t>
   </si>
   <si>
+    <t>19/11/2023</t>
+  </si>
+  <si>
     <t>NEHREBA</t>
   </si>
   <si>
     <t>Iryna</t>
   </si>
   <si>
+    <t>28/02/1987</t>
+  </si>
+  <si>
     <t>Ukraine</t>
   </si>
   <si>
+    <t>21/11/2024</t>
+  </si>
+  <si>
     <t>OMAR</t>
   </si>
   <si>
     <t>Mohammed</t>
   </si>
   <si>
+    <t>01/01/1994</t>
+  </si>
+  <si>
     <t>OVERCHENKO</t>
   </si>
   <si>
     <t>Aleksandrova</t>
   </si>
   <si>
+    <t>30/09/1971</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
     <t>PINTO</t>
   </si>
   <si>
     <t>Janet</t>
   </si>
   <si>
+    <t>23/02/1971</t>
+  </si>
+  <si>
     <t>Pérou</t>
   </si>
   <si>
@@ -217,6 +322,9 @@
     <t>Daleep</t>
   </si>
   <si>
+    <t>01/09/1984</t>
+  </si>
+  <si>
     <t>Afghanistan</t>
   </si>
   <si>
@@ -226,6 +334,9 @@
     <t>Ahmed</t>
   </si>
   <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
     <t>Somalie</t>
   </si>
   <si>
@@ -235,13 +346,22 @@
     <t>Malika</t>
   </si>
   <si>
+    <t>01/09/1956</t>
+  </si>
+  <si>
     <t>Espagne</t>
   </si>
   <si>
+    <t>16/11/2023</t>
+  </si>
+  <si>
     <t>YLDIRIM DOGAN</t>
   </si>
   <si>
     <t>Ozgun</t>
+  </si>
+  <si>
+    <t>01/07/1979</t>
   </si>
   <si>
     <t>Turquie</t>
@@ -802,10 +922,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -813,25 +933,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -839,25 +959,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -865,25 +985,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -891,25 +1011,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="G8" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -917,25 +1037,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -943,25 +1063,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -969,25 +1089,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -995,25 +1115,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1021,25 +1141,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1047,25 +1167,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1073,25 +1193,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1099,25 +1219,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1125,25 +1245,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1151,25 +1271,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1177,25 +1297,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1203,25 +1323,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1229,25 +1349,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1255,25 +1375,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1281,25 +1401,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1307,25 +1427,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1333,25 +1453,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1359,25 +1479,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
